--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -478,7 +478,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 14:39</t>
+          <t>2026-05-08 16:05</t>
         </is>
       </c>
     </row>
@@ -544,11 +544,11 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7500</v>
+        <v>3250</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>ค่าขนส่งงานขากลับ (manual — ไม่มีใน GPS)</t>
+          <t>ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก</t>
         </is>
       </c>
       <c r="E5" s="6" t="n"/>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:05</t>
+          <t>2026-05-08 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -104,7 +104,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>3250</v>
+        <v>3273.09</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:26</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:26</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual_Return_Trips" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Manual_Return_Trips" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Return_Trips'!$A$4:$F$5</definedName>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-05-26 13:09</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:09</t>
+          <t>2026-05-26 13:16</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:16</t>
+          <t>2026-05-26 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:20</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>3273.09</v>
+        <v>3250</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Manual_Return_Trips" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Return_Trips'!$A$4:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Return_Trips'!$A$4:$F$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F7FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -105,6 +110,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,13 +486,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -498,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:49</t>
         </is>
       </c>
     </row>
@@ -554,8 +568,168 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
     </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>3632</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>ตีเปล่าไป P&amp;G 50%</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>3584</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>3584</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับเพิ่ม 50% (base คิด ตีเปล่า+BH#1 = 1 เที่ยวแล้ว)</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F5"/>
+  <autoFilter ref="A4:F13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Manual_Return_Trips" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Return_Trips'!$A$4:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Return_Trips'!$A$4:$F$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:49</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
@@ -662,7 +662,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
         </is>
       </c>
       <c r="E10" s="9" t="n"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>BH ขากลับเพิ่ม 50% (base คิด ตีเปล่า+BH#1 = 1 เที่ยวแล้ว)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
@@ -690,11 +690,11 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
@@ -710,11 +710,11 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
@@ -722,14 +722,54 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว)</t>
         </is>
       </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
     </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F13"/>
+  <autoFilter ref="A4:F15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Manual_Return_Trips" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Return_Trips'!$A$4:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Return_Trips'!$A$4:$F$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>
@@ -550,19 +550,19 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>3250</v>
+        <v>3632</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก</t>
+          <t>ตีเปล่าไป P&amp;G 50%</t>
         </is>
       </c>
       <c r="E5" s="6" t="n"/>
@@ -570,19 +570,19 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46143</v>
+        <v>46152</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>3632</v>
+        <v>3584</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>ตีเปล่าไป P&amp;G 50%</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
         </is>
       </c>
       <c r="E6" s="9" t="n"/>
@@ -590,7 +590,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
@@ -610,15 +610,15 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>3584</v>
+        <v>3728</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
@@ -642,7 +642,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
         </is>
       </c>
       <c r="E9" s="6" t="n"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
         </is>
       </c>
       <c r="E10" s="9" t="n"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
@@ -694,7 +694,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
@@ -702,7 +702,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว)</t>
         </is>
       </c>
       <c r="E12" s="9" t="n"/>
@@ -710,7 +710,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
         </is>
       </c>
       <c r="E13" s="6" t="n"/>
@@ -730,11 +730,11 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
@@ -748,28 +748,8 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>71-8009</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>3728</v>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F15"/>
+  <autoFilter ref="A4:F14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Manual_Return_Trips" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Return_Trips'!$A$4:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Return_Trips'!$A$4:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 18:21</t>
+          <t>2026-08-04 14:01</t>
         </is>
       </c>
     </row>
@@ -550,19 +550,19 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46143</v>
+        <v>46204</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>3632</v>
+        <v>3488</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>ตีเปล่าไป P&amp;G 50%</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 1/7 11พาเลท = ชีท LCB 1/7 13พาเลท — เหตุการณ์เดียว นับครั้งเดียว)</t>
         </is>
       </c>
       <c r="E5" s="6" t="n"/>
@@ -570,7 +570,7 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46152</v>
+        <v>46207</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>3584</v>
+        <v>3488</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท LCB 4/7 มีของกลับ 12 พาเลท)</t>
         </is>
       </c>
       <c r="E6" s="9" t="n"/>
@@ -590,19 +590,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46153</v>
+        <v>46208</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>3584</v>
+        <v>3488</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท LCB 5/7 มีของกลับ 10 พาเลท)</t>
         </is>
       </c>
       <c r="E7" s="6" t="n"/>
@@ -610,19 +610,19 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46162</v>
+        <v>46211</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>3728</v>
+        <v>3344</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 8/7 — ไม่ระบุจำนวนพาเลท)</t>
         </is>
       </c>
       <c r="E8" s="9" t="n"/>
@@ -630,19 +630,19 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46162</v>
+        <v>46211</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3728</v>
+        <v>3344</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท LCB 8/7 มีของกลับ 14 พาเลท)</t>
         </is>
       </c>
       <c r="E9" s="6" t="n"/>
@@ -650,19 +650,19 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46162</v>
+        <v>46212</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3728</v>
+        <v>3344</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท LCB 9/7 มีของกลับ 10 พาเลท)</t>
         </is>
       </c>
       <c r="E10" s="9" t="n"/>
@@ -670,19 +670,19 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46162</v>
+        <v>46213</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>3728</v>
+        <v>3344</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 10/7, 21 พาเลท)</t>
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
@@ -690,19 +690,19 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>46162</v>
+        <v>46213</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>3728</v>
+        <v>3344</v>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 10/7, 10 พาเลท)</t>
         </is>
       </c>
       <c r="E12" s="9" t="n"/>
@@ -710,7 +710,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46163</v>
+        <v>46214</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
@@ -718,11 +718,11 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>3728</v>
+        <v>3344</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 11/7, 19 พาเลท)</t>
         </is>
       </c>
       <c r="E13" s="6" t="n"/>
@@ -730,26 +730,326 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46164</v>
+        <v>46216</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>3728</v>
+        <v>3344</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท LCB 13/7 มีของกลับ 2 พาเลท)</t>
         </is>
       </c>
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="n"/>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>3344</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 16/7, 10 พาเลท)</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>3344</v>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 16/7, 4 พาเลท)</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>3344</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 17/7, 7 พาเลท)</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>3344</v>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 20/7, 20 พาเลท T9874551)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>3344</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 20/7, 10 พาเลท = ชีท LCB 20/7 — เหตุการณ์เดียว)</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>3344</v>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 21/7, 18 พาเลท)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>3344</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 21/7, TO-OTL17062 เต็มตู้)</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>3392</v>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 22/7, 17 พาเลท)</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>3440</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 23/7, 10 พาเลท T9874565 = ชีท LCB 23/7)</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>3440</v>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 24/7, 16 พาเลท = ชีท LCB 24/7)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>3440</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 24/7 9 พาเลท = ชีท LCB 24/7 6 พาเลท — เหตุการณ์เดียว จำนวนพาเลทสองชีทไม่ตรงกัน)</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>3440</v>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 25/7, 20 พาเลท T9874597)</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>3440</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 25/7, 20 พาเลท — ชีท LCB ลง 24/7 มีของกลับ 20 พาเลท = เหตุการณ์เดียว ข้ามคืน นับครั้งเดียวตามวันชีท AYU)</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>3440</v>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 27/7, 16 พาเลท = ชีท LCB 27/7)</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>3440</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (ชีท AYU 31/7, 11 พาเลท TO-OTL17903)</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F14"/>
+  <autoFilter ref="A4:F29"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:01</t>
+          <t>2026-08-04 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:33</t>
+          <t>2026-08-04 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:11</t>
+          <t>2026-08-05 14:34</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 14:34</t>
+          <t>2026-08-07 15:55</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 15:55</t>
+          <t>2026-08-09 10:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/11_Manual_Return_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:57</t>
+          <t>2026-08-09 11:52</t>
         </is>
       </c>
     </row>
